--- a/public/exports-60-250/58271713.xlsx
+++ b/public/exports-60-250/58271713.xlsx
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027403</t>
+          <t xml:space="preserve">200027402</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">310007202</t>
+          <t xml:space="preserve">310007201</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
